--- a/data/nzd0140/nzd0140.xlsx
+++ b/data/nzd0140/nzd0140.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J339"/>
+  <dimension ref="A1:J340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12640,6 +12640,42 @@
         <v>388.36</v>
       </c>
       <c r="J339" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>389.01</v>
+      </c>
+      <c r="C340" t="n">
+        <v>387.55</v>
+      </c>
+      <c r="D340" t="n">
+        <v>394.32</v>
+      </c>
+      <c r="E340" t="n">
+        <v>386.27</v>
+      </c>
+      <c r="F340" t="n">
+        <v>382.01</v>
+      </c>
+      <c r="G340" t="n">
+        <v>378.17</v>
+      </c>
+      <c r="H340" t="n">
+        <v>384.94</v>
+      </c>
+      <c r="I340" t="n">
+        <v>388.92</v>
+      </c>
+      <c r="J340" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12656,7 +12692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16199,6 +16235,16 @@
       </c>
       <c r="B354" t="n">
         <v>-0.45</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>-0.48</v>
       </c>
     </row>
   </sheetData>
@@ -16367,28 +16413,28 @@
         <v>0.1057</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09153401620977923</v>
+        <v>-0.09292808258410529</v>
       </c>
       <c r="J2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02843116429286896</v>
+        <v>0.02942768652413341</v>
       </c>
       <c r="M2" t="n">
-        <v>2.6554735130133</v>
+        <v>2.65352040120914</v>
       </c>
       <c r="N2" t="n">
-        <v>15.69658775627016</v>
+        <v>15.66714073762558</v>
       </c>
       <c r="O2" t="n">
-        <v>3.961891941518618</v>
+        <v>3.958173914524926</v>
       </c>
       <c r="P2" t="n">
-        <v>393.8093234126361</v>
+        <v>393.8236673809118</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16445,28 +16491,28 @@
         <v>0.1009</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1220259383316097</v>
+        <v>-0.1251262129250974</v>
       </c>
       <c r="J3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0608056377682592</v>
+        <v>0.06371808193850592</v>
       </c>
       <c r="M3" t="n">
-        <v>2.497799795081417</v>
+        <v>2.503027390370434</v>
       </c>
       <c r="N3" t="n">
-        <v>12.60890074234742</v>
+        <v>12.65507017079554</v>
       </c>
       <c r="O3" t="n">
-        <v>3.55090139856733</v>
+        <v>3.557396543934277</v>
       </c>
       <c r="P3" t="n">
-        <v>396.0850991365652</v>
+        <v>396.1169987944538</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16523,28 +16569,28 @@
         <v>0.1948</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02130154352622149</v>
+        <v>-0.0216924994945345</v>
       </c>
       <c r="J4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002279231382189217</v>
+        <v>0.002378127383495854</v>
       </c>
       <c r="M4" t="n">
-        <v>2.564291866486478</v>
+        <v>2.558584739442908</v>
       </c>
       <c r="N4" t="n">
-        <v>10.88940197128055</v>
+        <v>10.85860550419092</v>
       </c>
       <c r="O4" t="n">
-        <v>3.299909388343951</v>
+        <v>3.295239824988603</v>
       </c>
       <c r="P4" t="n">
-        <v>395.5524993694721</v>
+        <v>395.5565220330338</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16601,28 +16647,28 @@
         <v>0.1976</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05399102091296484</v>
+        <v>-0.05860874255632659</v>
       </c>
       <c r="J5" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K5" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009306685698628248</v>
+        <v>0.01089968374523098</v>
       </c>
       <c r="M5" t="n">
-        <v>3.242305677664604</v>
+        <v>3.257195332709694</v>
       </c>
       <c r="N5" t="n">
-        <v>17.01173266313754</v>
+        <v>17.14649139649208</v>
       </c>
       <c r="O5" t="n">
-        <v>4.124528174608284</v>
+        <v>4.140832210618064</v>
       </c>
       <c r="P5" t="n">
-        <v>395.6413826598</v>
+        <v>395.6888957868492</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16679,28 +16725,28 @@
         <v>0.1302</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05598956295232569</v>
+        <v>-0.06289628714263597</v>
       </c>
       <c r="J6" t="n">
+        <v>339</v>
+      </c>
+      <c r="K6" t="n">
         <v>338</v>
       </c>
-      <c r="K6" t="n">
-        <v>337</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.009405905362437794</v>
+        <v>0.01165216264566771</v>
       </c>
       <c r="M6" t="n">
-        <v>3.387504572774223</v>
+        <v>3.415639400002441</v>
       </c>
       <c r="N6" t="n">
-        <v>17.92219208765299</v>
+        <v>18.27705221065262</v>
       </c>
       <c r="O6" t="n">
-        <v>4.233461005802815</v>
+        <v>4.275166921963706</v>
       </c>
       <c r="P6" t="n">
-        <v>395.270580581634</v>
+        <v>395.3421568960089</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16757,28 +16803,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08860004713554416</v>
+        <v>-0.09571049680083085</v>
       </c>
       <c r="J7" t="n">
+        <v>339</v>
+      </c>
+      <c r="K7" t="n">
         <v>338</v>
       </c>
-      <c r="K7" t="n">
-        <v>337</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02295233108854444</v>
+        <v>0.02623704574489227</v>
       </c>
       <c r="M7" t="n">
-        <v>3.326785411150673</v>
+        <v>3.3562500234816</v>
       </c>
       <c r="N7" t="n">
-        <v>18.14005926997022</v>
+        <v>18.51869217093328</v>
       </c>
       <c r="O7" t="n">
-        <v>4.259114845830084</v>
+        <v>4.303335005659364</v>
       </c>
       <c r="P7" t="n">
-        <v>392.6390413395079</v>
+        <v>392.7127289179554</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16835,28 +16881,28 @@
         <v>0.1395</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1533724583583509</v>
+        <v>-0.1563527874291432</v>
       </c>
       <c r="J8" t="n">
+        <v>339</v>
+      </c>
+      <c r="K8" t="n">
         <v>338</v>
       </c>
-      <c r="K8" t="n">
-        <v>337</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.09536664780722537</v>
+        <v>0.09874668941961529</v>
       </c>
       <c r="M8" t="n">
-        <v>2.743748974292618</v>
+        <v>2.752806157698287</v>
       </c>
       <c r="N8" t="n">
-        <v>12.1130268167869</v>
+        <v>12.15313832014498</v>
       </c>
       <c r="O8" t="n">
-        <v>3.480377395741286</v>
+        <v>3.486135155174707</v>
       </c>
       <c r="P8" t="n">
-        <v>394.0449830448259</v>
+        <v>394.0758690284896</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16913,28 +16959,28 @@
         <v>0.1819</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1563556930183774</v>
+        <v>-0.1600873295446345</v>
       </c>
       <c r="J9" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K9" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06470154875633516</v>
+        <v>0.06762110901874274</v>
       </c>
       <c r="M9" t="n">
-        <v>3.492738182222772</v>
+        <v>3.501758896336294</v>
       </c>
       <c r="N9" t="n">
-        <v>19.37421976061204</v>
+        <v>19.43784337511664</v>
       </c>
       <c r="O9" t="n">
-        <v>4.401615585283663</v>
+        <v>4.408836963998175</v>
       </c>
       <c r="P9" t="n">
-        <v>399.4464676809922</v>
+        <v>399.4848636117276</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16972,7 +17018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J339"/>
+  <dimension ref="A1:J340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34591,6 +34637,58 @@
         </is>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-36.602091120032206,175.5431483317068</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>-36.60256502946498,175.54367257205413</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>-36.60273473962117,175.54445455709197</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>-36.60297110341118,175.5452563930021</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-36.60305182484203,175.54611161767954</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>-36.6030698594587,175.54698830223305</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>-36.60291038221773,175.54783601940716</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>-36.60269584484705,175.54867548416348</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0140/nzd0140.xlsx
+++ b/data/nzd0140/nzd0140.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J340"/>
+  <dimension ref="A1:J341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12678,6 +12678,42 @@
       <c r="J340" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>390.57</v>
+      </c>
+      <c r="C341" t="n">
+        <v>388.32</v>
+      </c>
+      <c r="D341" t="n">
+        <v>392.75</v>
+      </c>
+      <c r="E341" t="n">
+        <v>385.96</v>
+      </c>
+      <c r="F341" t="n">
+        <v>383.7</v>
+      </c>
+      <c r="G341" t="n">
+        <v>381.71</v>
+      </c>
+      <c r="H341" t="n">
+        <v>386.39</v>
+      </c>
+      <c r="I341" t="n">
+        <v>392.7</v>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B355"/>
+  <dimension ref="A1:B356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16245,6 +16281,16 @@
       </c>
       <c r="B355" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -16413,28 +16459,28 @@
         <v>0.1057</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09292808258410529</v>
+        <v>-0.09339815131204141</v>
       </c>
       <c r="J2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02942768652413341</v>
+        <v>0.02989803449046624</v>
       </c>
       <c r="M2" t="n">
-        <v>2.65352040120914</v>
+        <v>2.647667224887297</v>
       </c>
       <c r="N2" t="n">
-        <v>15.66714073762558</v>
+        <v>15.62296880012023</v>
       </c>
       <c r="O2" t="n">
-        <v>3.958173914524926</v>
+        <v>3.952590138139829</v>
       </c>
       <c r="P2" t="n">
-        <v>393.8236673809118</v>
+        <v>393.8285279838964</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16491,28 +16537,28 @@
         <v>0.1009</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1251262129250974</v>
+        <v>-0.1277460840378209</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06371808193850592</v>
+        <v>0.06634005237336171</v>
       </c>
       <c r="M3" t="n">
-        <v>2.503027390370434</v>
+        <v>2.506388456136691</v>
       </c>
       <c r="N3" t="n">
-        <v>12.65507017079554</v>
+        <v>12.67711325231649</v>
       </c>
       <c r="O3" t="n">
-        <v>3.557396543934277</v>
+        <v>3.560493400122585</v>
       </c>
       <c r="P3" t="n">
-        <v>396.1169987944538</v>
+        <v>396.1440887763931</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16569,28 +16615,28 @@
         <v>0.1948</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0216924994945345</v>
+        <v>-0.02298921438199151</v>
       </c>
       <c r="J4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002378127383495854</v>
+        <v>0.002683593023753095</v>
       </c>
       <c r="M4" t="n">
-        <v>2.558584739442908</v>
+        <v>2.55719751309215</v>
       </c>
       <c r="N4" t="n">
-        <v>10.85860550419092</v>
+        <v>10.84118684378075</v>
       </c>
       <c r="O4" t="n">
-        <v>3.295239824988603</v>
+        <v>3.292595760760916</v>
       </c>
       <c r="P4" t="n">
-        <v>395.5565220330338</v>
+        <v>395.56993031969</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16647,28 +16693,28 @@
         <v>0.1976</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05860874255632659</v>
+        <v>-0.06336199596683502</v>
       </c>
       <c r="J5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01089968374523098</v>
+        <v>0.01265365091883297</v>
       </c>
       <c r="M5" t="n">
-        <v>3.257195332709694</v>
+        <v>3.27272730908027</v>
       </c>
       <c r="N5" t="n">
-        <v>17.14649139649208</v>
+        <v>17.29114026566254</v>
       </c>
       <c r="O5" t="n">
-        <v>4.140832210618064</v>
+        <v>4.158261687972817</v>
       </c>
       <c r="P5" t="n">
-        <v>395.6888957868492</v>
+        <v>395.7380453608181</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16725,28 +16771,28 @@
         <v>0.1302</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06289628714263597</v>
+        <v>-0.06874673853447059</v>
       </c>
       <c r="J6" t="n">
+        <v>340</v>
+      </c>
+      <c r="K6" t="n">
         <v>339</v>
       </c>
-      <c r="K6" t="n">
-        <v>338</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01165216264566771</v>
+        <v>0.01376019611557133</v>
       </c>
       <c r="M6" t="n">
-        <v>3.415639400002441</v>
+        <v>3.438410673787896</v>
       </c>
       <c r="N6" t="n">
-        <v>18.27705221065262</v>
+        <v>18.51448821554333</v>
       </c>
       <c r="O6" t="n">
-        <v>4.275166921963706</v>
+        <v>4.302846524748858</v>
       </c>
       <c r="P6" t="n">
-        <v>395.3421568960089</v>
+        <v>395.4030840887969</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16803,28 +16849,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09571049680083085</v>
+        <v>-0.100684697439241</v>
       </c>
       <c r="J7" t="n">
+        <v>340</v>
+      </c>
+      <c r="K7" t="n">
         <v>339</v>
       </c>
-      <c r="K7" t="n">
-        <v>338</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02623704574489227</v>
+        <v>0.02881543754804627</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3562500234816</v>
+        <v>3.374128368116727</v>
       </c>
       <c r="N7" t="n">
-        <v>18.51869217093328</v>
+        <v>18.67467708591239</v>
       </c>
       <c r="O7" t="n">
-        <v>4.303335005659364</v>
+        <v>4.321420725399506</v>
       </c>
       <c r="P7" t="n">
-        <v>392.7127289179554</v>
+        <v>392.7645307467316</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16881,28 +16927,28 @@
         <v>0.1395</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1563527874291432</v>
+        <v>-0.1584448524001162</v>
       </c>
       <c r="J8" t="n">
+        <v>340</v>
+      </c>
+      <c r="K8" t="n">
         <v>339</v>
       </c>
-      <c r="K8" t="n">
-        <v>338</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.09874668941961529</v>
+        <v>0.1014410628439096</v>
       </c>
       <c r="M8" t="n">
-        <v>2.752806157698287</v>
+        <v>2.756890296802825</v>
       </c>
       <c r="N8" t="n">
-        <v>12.15313832014498</v>
+        <v>12.1545436079656</v>
       </c>
       <c r="O8" t="n">
-        <v>3.486135155174707</v>
+        <v>3.486336703183672</v>
       </c>
       <c r="P8" t="n">
-        <v>394.0758690284896</v>
+        <v>394.0976560047885</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16959,28 +17005,28 @@
         <v>0.1819</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1600873295446345</v>
+        <v>-0.161584966342497</v>
       </c>
       <c r="J9" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K9" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06762110901874274</v>
+        <v>0.0691498622315514</v>
       </c>
       <c r="M9" t="n">
-        <v>3.501758896336294</v>
+        <v>3.499182152624402</v>
       </c>
       <c r="N9" t="n">
-        <v>19.43784337511664</v>
+        <v>19.40003939370451</v>
       </c>
       <c r="O9" t="n">
-        <v>4.408836963998175</v>
+        <v>4.404547581046719</v>
       </c>
       <c r="P9" t="n">
-        <v>399.4848636117276</v>
+        <v>399.5003494704054</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -17018,7 +17064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J340"/>
+  <dimension ref="A1:J341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34689,6 +34735,58 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-36.60208127819821,175.5431607755972</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-36.60255917213745,175.5436771820732</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-36.60274830938758,175.54444960682045</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-36.6029738709574,175.54525592753694</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-36.60303659917033,175.54611162198702</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-36.603038134646205,175.54698424749017</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-36.602897631607405,175.5478324949182</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>-36.60266307763453,175.54866397879417</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0140/nzd0140.xlsx
+++ b/data/nzd0140/nzd0140.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J341"/>
+  <dimension ref="A1:J343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12712,6 +12712,78 @@
         <v>392.7</v>
       </c>
       <c r="J341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>386.92</v>
+      </c>
+      <c r="C342" t="n">
+        <v>387.39</v>
+      </c>
+      <c r="D342" t="n">
+        <v>391.88</v>
+      </c>
+      <c r="E342" t="n">
+        <v>386.34</v>
+      </c>
+      <c r="F342" t="n">
+        <v>384.92</v>
+      </c>
+      <c r="G342" t="n">
+        <v>382.71</v>
+      </c>
+      <c r="H342" t="n">
+        <v>386.85</v>
+      </c>
+      <c r="I342" t="n">
+        <v>392.52</v>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>386.72</v>
+      </c>
+      <c r="C343" t="n">
+        <v>389.15</v>
+      </c>
+      <c r="D343" t="n">
+        <v>393.19</v>
+      </c>
+      <c r="E343" t="n">
+        <v>389.47</v>
+      </c>
+      <c r="F343" t="n">
+        <v>388.41</v>
+      </c>
+      <c r="G343" t="n">
+        <v>386.29</v>
+      </c>
+      <c r="H343" t="n">
+        <v>388.89</v>
+      </c>
+      <c r="I343" t="n">
+        <v>396.05</v>
+      </c>
+      <c r="J343" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12728,7 +12800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B356"/>
+  <dimension ref="A1:B358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16291,6 +16363,26 @@
       </c>
       <c r="B356" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -16459,28 +16551,28 @@
         <v>0.1057</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09339815131204141</v>
+        <v>-0.09861865514246311</v>
       </c>
       <c r="J2" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K2" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02989803449046624</v>
+        <v>0.03338313108063584</v>
       </c>
       <c r="M2" t="n">
-        <v>2.647667224887297</v>
+        <v>2.654497345395039</v>
       </c>
       <c r="N2" t="n">
-        <v>15.62296880012023</v>
+        <v>15.65025895924268</v>
       </c>
       <c r="O2" t="n">
-        <v>3.952590138139829</v>
+        <v>3.956040818702795</v>
       </c>
       <c r="P2" t="n">
-        <v>393.8285279838964</v>
+        <v>393.882694138482</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16537,28 +16629,28 @@
         <v>0.1009</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1277460840378209</v>
+        <v>-0.1329178695768231</v>
       </c>
       <c r="J3" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K3" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06634005237336171</v>
+        <v>0.07163710771480414</v>
       </c>
       <c r="M3" t="n">
-        <v>2.506388456136691</v>
+        <v>2.513327677629072</v>
       </c>
       <c r="N3" t="n">
-        <v>12.67711325231649</v>
+        <v>12.72396738891468</v>
       </c>
       <c r="O3" t="n">
-        <v>3.560493400122585</v>
+        <v>3.567067056969168</v>
       </c>
       <c r="P3" t="n">
-        <v>396.1440887763931</v>
+        <v>396.197743714165</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16615,28 +16707,28 @@
         <v>0.1948</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02298921438199151</v>
+        <v>-0.02577898876314358</v>
       </c>
       <c r="J4" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K4" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002683593023753095</v>
+        <v>0.003403565006866782</v>
       </c>
       <c r="M4" t="n">
-        <v>2.55719751309215</v>
+        <v>2.555360498460821</v>
       </c>
       <c r="N4" t="n">
-        <v>10.84118684378075</v>
+        <v>10.81416789889355</v>
       </c>
       <c r="O4" t="n">
-        <v>3.292595760760916</v>
+        <v>3.288490215721121</v>
       </c>
       <c r="P4" t="n">
-        <v>395.56993031969</v>
+        <v>395.5988719277909</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16693,28 +16785,28 @@
         <v>0.1976</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06336199596683502</v>
+        <v>-0.0704381316664498</v>
       </c>
       <c r="J5" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K5" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01265365091883297</v>
+        <v>0.01557990714546054</v>
       </c>
       <c r="M5" t="n">
-        <v>3.27272730908027</v>
+        <v>3.290741820886182</v>
       </c>
       <c r="N5" t="n">
-        <v>17.29114026566254</v>
+        <v>17.42237409610861</v>
       </c>
       <c r="O5" t="n">
-        <v>4.158261687972817</v>
+        <v>4.174011750834994</v>
       </c>
       <c r="P5" t="n">
-        <v>395.7380453608181</v>
+        <v>395.811454960036</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16771,28 +16863,28 @@
         <v>0.1302</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06874673853447059</v>
+        <v>-0.0767665377772615</v>
       </c>
       <c r="J6" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K6" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01376019611557133</v>
+        <v>0.01704786462985752</v>
       </c>
       <c r="M6" t="n">
-        <v>3.438410673787896</v>
+        <v>3.464306876386146</v>
       </c>
       <c r="N6" t="n">
-        <v>18.51448821554333</v>
+        <v>18.69978620315031</v>
       </c>
       <c r="O6" t="n">
-        <v>4.302846524748858</v>
+        <v>4.324324941901373</v>
       </c>
       <c r="P6" t="n">
-        <v>395.4030840887969</v>
+        <v>395.4868758848669</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16849,28 +16941,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.100684697439241</v>
+        <v>-0.1071782171326255</v>
       </c>
       <c r="J7" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K7" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02881543754804627</v>
+        <v>0.03259162391848625</v>
       </c>
       <c r="M7" t="n">
-        <v>3.374128368116727</v>
+        <v>3.391469724106489</v>
       </c>
       <c r="N7" t="n">
-        <v>18.67467708591239</v>
+        <v>18.76494304989903</v>
       </c>
       <c r="O7" t="n">
-        <v>4.321420725399506</v>
+        <v>4.331852150050718</v>
       </c>
       <c r="P7" t="n">
-        <v>392.7645307467316</v>
+        <v>392.8323735606277</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16927,28 +17019,28 @@
         <v>0.1395</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1584448524001162</v>
+        <v>-0.1608133259249214</v>
       </c>
       <c r="J8" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K8" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1014410628439096</v>
+        <v>0.1051381794104899</v>
       </c>
       <c r="M8" t="n">
-        <v>2.756890296802825</v>
+        <v>2.754570561121666</v>
       </c>
       <c r="N8" t="n">
-        <v>12.1545436079656</v>
+        <v>12.11350842495374</v>
       </c>
       <c r="O8" t="n">
-        <v>3.486336703183672</v>
+        <v>3.480446584125914</v>
       </c>
       <c r="P8" t="n">
-        <v>394.0976560047885</v>
+        <v>394.1223990760476</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -17005,28 +17097,28 @@
         <v>0.1819</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.161584966342497</v>
+        <v>-0.1626718847123795</v>
       </c>
       <c r="J9" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K9" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0691498622315514</v>
+        <v>0.07076890033296912</v>
       </c>
       <c r="M9" t="n">
-        <v>3.499182152624402</v>
+        <v>3.489150318594229</v>
       </c>
       <c r="N9" t="n">
-        <v>19.40003939370451</v>
+        <v>19.31000384685605</v>
       </c>
       <c r="O9" t="n">
-        <v>4.404547581046719</v>
+        <v>4.394314946252265</v>
       </c>
       <c r="P9" t="n">
-        <v>399.5003494704054</v>
+        <v>399.5116164774186</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -17064,7 +17156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J341"/>
+  <dimension ref="A1:J343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34787,6 +34879,110 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-36.60210430556434,175.54313166007947</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-36.60256624657198,175.54367161412802</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-36.60275582893959,175.5444468636757</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-36.602970478481396,175.54525649810714</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-36.60302560785701,175.5461116250967</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-36.60302917283469,175.54698310208337</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-36.60289358658616,175.54783137680474</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-36.60266463797802,175.54866452666866</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-36.60210556733764,175.54313006470815</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-36.6025528583946,175.54368215131373</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-36.60274450639573,175.54445099415784</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-36.602942535191985,175.54526119780215</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-36.60299416549341,175.54611163399287</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-36.602997089549206,175.54697900152954</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-36.60287564779609,175.54782641821615</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-36.602634037907755,175.5486537822455</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0140/nzd0140.xlsx
+++ b/data/nzd0140/nzd0140.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J343"/>
+  <dimension ref="A1:J345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12784,6 +12784,78 @@
         <v>396.05</v>
       </c>
       <c r="J343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>386.97</v>
+      </c>
+      <c r="C344" t="n">
+        <v>389.91</v>
+      </c>
+      <c r="D344" t="n">
+        <v>388.9</v>
+      </c>
+      <c r="E344" t="n">
+        <v>389.39</v>
+      </c>
+      <c r="F344" t="n">
+        <v>391</v>
+      </c>
+      <c r="G344" t="n">
+        <v>389.21</v>
+      </c>
+      <c r="H344" t="n">
+        <v>390.37</v>
+      </c>
+      <c r="I344" t="n">
+        <v>395.18</v>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>387.18</v>
+      </c>
+      <c r="C345" t="n">
+        <v>390.02</v>
+      </c>
+      <c r="D345" t="n">
+        <v>390.13</v>
+      </c>
+      <c r="E345" t="n">
+        <v>389.99</v>
+      </c>
+      <c r="F345" t="n">
+        <v>391.07</v>
+      </c>
+      <c r="G345" t="n">
+        <v>388.74</v>
+      </c>
+      <c r="H345" t="n">
+        <v>389.62</v>
+      </c>
+      <c r="I345" t="n">
+        <v>395.21</v>
+      </c>
+      <c r="J345" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12800,7 +12872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16383,6 +16455,26 @@
       </c>
       <c r="B358" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -16551,28 +16643,28 @@
         <v>0.1057</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09861865514246311</v>
+        <v>-0.1033991721495827</v>
       </c>
       <c r="J2" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K2" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03338313108063584</v>
+        <v>0.03679674769639052</v>
       </c>
       <c r="M2" t="n">
-        <v>2.654497345395039</v>
+        <v>2.659361229681868</v>
       </c>
       <c r="N2" t="n">
-        <v>15.65025895924268</v>
+        <v>15.65972323174984</v>
       </c>
       <c r="O2" t="n">
-        <v>3.956040818702795</v>
+        <v>3.957236817749203</v>
       </c>
       <c r="P2" t="n">
-        <v>393.882694138482</v>
+        <v>393.9325591177172</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16629,28 +16721,28 @@
         <v>0.1009</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1329178695768231</v>
+        <v>-0.1360053105596383</v>
       </c>
       <c r="J3" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K3" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07163710771480414</v>
+        <v>0.07540156438926704</v>
       </c>
       <c r="M3" t="n">
-        <v>2.513327677629072</v>
+        <v>2.511773439854952</v>
       </c>
       <c r="N3" t="n">
-        <v>12.72396738891468</v>
+        <v>12.69188078817585</v>
       </c>
       <c r="O3" t="n">
-        <v>3.567067056969168</v>
+        <v>3.562566601226685</v>
       </c>
       <c r="P3" t="n">
-        <v>396.197743714165</v>
+        <v>396.2299485792939</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16707,28 +16799,28 @@
         <v>0.1948</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02577898876314358</v>
+        <v>-0.03193391123333323</v>
       </c>
       <c r="J4" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003403565006866782</v>
+        <v>0.005198293532164056</v>
       </c>
       <c r="M4" t="n">
-        <v>2.555360498460821</v>
+        <v>2.569427617548949</v>
       </c>
       <c r="N4" t="n">
-        <v>10.81416789889355</v>
+        <v>10.91996894654574</v>
       </c>
       <c r="O4" t="n">
-        <v>3.288490215721121</v>
+        <v>3.304537629766944</v>
       </c>
       <c r="P4" t="n">
-        <v>395.5988719277909</v>
+        <v>395.6630675930527</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16785,28 +16877,28 @@
         <v>0.1976</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0704381316664498</v>
+        <v>-0.07529129704249292</v>
       </c>
       <c r="J5" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K5" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01557990714546054</v>
+        <v>0.01787809467059476</v>
       </c>
       <c r="M5" t="n">
-        <v>3.290741820886182</v>
+        <v>3.296996660683871</v>
       </c>
       <c r="N5" t="n">
-        <v>17.42237409610861</v>
+        <v>17.42509586389912</v>
       </c>
       <c r="O5" t="n">
-        <v>4.174011750834994</v>
+        <v>4.174337775491955</v>
       </c>
       <c r="P5" t="n">
-        <v>395.811454960036</v>
+        <v>395.8620754594484</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16863,28 +16955,28 @@
         <v>0.1302</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0767665377772615</v>
+        <v>-0.07954836147992528</v>
       </c>
       <c r="J6" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K6" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01704786462985752</v>
+        <v>0.01847971029054019</v>
       </c>
       <c r="M6" t="n">
-        <v>3.464306876386146</v>
+        <v>3.460070166979522</v>
       </c>
       <c r="N6" t="n">
-        <v>18.69978620315031</v>
+        <v>18.6242712387131</v>
       </c>
       <c r="O6" t="n">
-        <v>4.324324941901373</v>
+        <v>4.315584692566362</v>
       </c>
       <c r="P6" t="n">
-        <v>395.4868758848669</v>
+        <v>395.5160982286322</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16941,28 +17033,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1071782171326255</v>
+        <v>-0.1083496187181136</v>
       </c>
       <c r="J7" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K7" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03259162391848625</v>
+        <v>0.0336847454345115</v>
       </c>
       <c r="M7" t="n">
-        <v>3.391469724106489</v>
+        <v>3.378310616938016</v>
       </c>
       <c r="N7" t="n">
-        <v>18.76494304989903</v>
+        <v>18.66177840797157</v>
       </c>
       <c r="O7" t="n">
-        <v>4.331852150050718</v>
+        <v>4.319928055879122</v>
       </c>
       <c r="P7" t="n">
-        <v>392.8323735606277</v>
+        <v>392.8446817369195</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17019,28 +17111,28 @@
         <v>0.1395</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1608133259249214</v>
+        <v>-0.1606608474946791</v>
       </c>
       <c r="J8" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K8" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1051381794104899</v>
+        <v>0.1061530896348746</v>
       </c>
       <c r="M8" t="n">
-        <v>2.754570561121666</v>
+        <v>2.740572207885894</v>
       </c>
       <c r="N8" t="n">
-        <v>12.11350842495374</v>
+        <v>12.04379345633051</v>
       </c>
       <c r="O8" t="n">
-        <v>3.480446584125914</v>
+        <v>3.470416899499325</v>
       </c>
       <c r="P8" t="n">
-        <v>394.1223990760476</v>
+        <v>394.1208016777498</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -17097,28 +17189,28 @@
         <v>0.1819</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1626718847123795</v>
+        <v>-0.1626806026607004</v>
       </c>
       <c r="J9" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K9" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07076890033296912</v>
+        <v>0.07161301650161744</v>
       </c>
       <c r="M9" t="n">
-        <v>3.489150318594229</v>
+        <v>3.468969791846584</v>
       </c>
       <c r="N9" t="n">
-        <v>19.31000384685605</v>
+        <v>19.19773859660985</v>
       </c>
       <c r="O9" t="n">
-        <v>4.394314946252265</v>
+        <v>4.381522406265869</v>
       </c>
       <c r="P9" t="n">
-        <v>399.5116164774186</v>
+        <v>399.5117072069353</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -17156,7 +17248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J343"/>
+  <dimension ref="A1:J345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34983,6 +35075,110 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-36.60210399012101,175.54313205892228</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-36.60254707713595,175.54368670146104</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-36.602781585565644,175.5444374676128</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-36.60294324939748,175.54526107768217</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-36.60297083147563,175.5461116405954</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-36.602970921059054,175.5469756569468</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-36.602862633379544,175.54782282081032</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-36.60264157956827,175.54865643030362</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-36.60210266525902,175.5431337340621</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-36.602546240374814,175.5436873600349</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-36.60277095447509,175.5444413458542</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-36.60293789285636,175.54526197858186</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>-36.60297020082651,175.54611164077386</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-36.60297513311057,175.546976195287</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-36.60286922852308,175.54782464381987</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-36.602641319511015,175.54865633899126</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0140/nzd0140.xlsx
+++ b/data/nzd0140/nzd0140.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J345"/>
+  <dimension ref="A1:J348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12858,6 +12858,114 @@
       <c r="J345" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>387.28</v>
+      </c>
+      <c r="C346" t="n">
+        <v>390.09</v>
+      </c>
+      <c r="D346" t="n">
+        <v>389.35</v>
+      </c>
+      <c r="E346" t="n">
+        <v>390.46</v>
+      </c>
+      <c r="F346" t="n">
+        <v>388.73</v>
+      </c>
+      <c r="G346" t="n">
+        <v>386.33</v>
+      </c>
+      <c r="H346" t="n">
+        <v>388.59</v>
+      </c>
+      <c r="I346" t="n">
+        <v>393.35</v>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>388.41</v>
+      </c>
+      <c r="C347" t="n">
+        <v>390.46</v>
+      </c>
+      <c r="D347" t="n">
+        <v>389.87</v>
+      </c>
+      <c r="E347" t="n">
+        <v>389.95</v>
+      </c>
+      <c r="F347" t="n">
+        <v>388.95</v>
+      </c>
+      <c r="G347" t="n">
+        <v>386.39</v>
+      </c>
+      <c r="H347" t="n">
+        <v>387.97</v>
+      </c>
+      <c r="I347" t="n">
+        <v>393.48</v>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>387.91</v>
+      </c>
+      <c r="C348" t="n">
+        <v>389.79</v>
+      </c>
+      <c r="D348" t="n">
+        <v>389.72</v>
+      </c>
+      <c r="E348" t="n">
+        <v>389.22</v>
+      </c>
+      <c r="F348" t="n">
+        <v>387.4</v>
+      </c>
+      <c r="G348" t="n">
+        <v>385.31</v>
+      </c>
+      <c r="H348" t="n">
+        <v>387.34</v>
+      </c>
+      <c r="I348" t="n">
+        <v>393.34</v>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12872,7 +12980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B360"/>
+  <dimension ref="A1:B363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16475,6 +16583,36 @@
       </c>
       <c r="B360" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>-0.64</v>
       </c>
     </row>
   </sheetData>
@@ -16643,28 +16781,28 @@
         <v>0.1057</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1033991721495827</v>
+        <v>-0.1089721190552594</v>
       </c>
       <c r="J2" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K2" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03679674769639052</v>
+        <v>0.04121054382977174</v>
       </c>
       <c r="M2" t="n">
-        <v>2.659361229681868</v>
+        <v>2.66017704360674</v>
       </c>
       <c r="N2" t="n">
-        <v>15.65972323174984</v>
+        <v>15.61819678760648</v>
       </c>
       <c r="O2" t="n">
-        <v>3.957236817749203</v>
+        <v>3.951986435655679</v>
       </c>
       <c r="P2" t="n">
-        <v>393.9325591177172</v>
+        <v>393.9910575633277</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16721,28 +16859,28 @@
         <v>0.1009</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1360053105596383</v>
+        <v>-0.140206837836549</v>
       </c>
       <c r="J3" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K3" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07540156438926704</v>
+        <v>0.08084191273691477</v>
       </c>
       <c r="M3" t="n">
-        <v>2.511773439854952</v>
+        <v>2.50764345860744</v>
       </c>
       <c r="N3" t="n">
-        <v>12.69188078817585</v>
+        <v>12.63505729837078</v>
       </c>
       <c r="O3" t="n">
-        <v>3.562566601226685</v>
+        <v>3.554582577233335</v>
       </c>
       <c r="P3" t="n">
-        <v>396.2299485792939</v>
+        <v>396.2740582498038</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16799,28 +16937,28 @@
         <v>0.1948</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03193391123333323</v>
+        <v>-0.04063931809284634</v>
       </c>
       <c r="J4" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K4" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005198293532164056</v>
+        <v>0.008378126045600842</v>
       </c>
       <c r="M4" t="n">
-        <v>2.569427617548949</v>
+        <v>2.588598994815945</v>
       </c>
       <c r="N4" t="n">
-        <v>10.91996894654574</v>
+        <v>11.05038036052482</v>
       </c>
       <c r="O4" t="n">
-        <v>3.304537629766944</v>
+        <v>3.324211238854237</v>
       </c>
       <c r="P4" t="n">
-        <v>395.6630675930527</v>
+        <v>395.7544541611751</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16877,28 +17015,28 @@
         <v>0.1976</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07529129704249292</v>
+        <v>-0.08199711011431036</v>
       </c>
       <c r="J5" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K5" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01787809467059476</v>
+        <v>0.02136541328138541</v>
       </c>
       <c r="M5" t="n">
-        <v>3.296996660683871</v>
+        <v>3.303404937571221</v>
       </c>
       <c r="N5" t="n">
-        <v>17.42509586389912</v>
+        <v>17.40971051581432</v>
       </c>
       <c r="O5" t="n">
-        <v>4.174337775491955</v>
+        <v>4.172494519566721</v>
       </c>
       <c r="P5" t="n">
-        <v>395.8620754594484</v>
+        <v>395.9324842944035</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16955,28 +17093,28 @@
         <v>0.1302</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07954836147992528</v>
+        <v>-0.08811196425305361</v>
       </c>
       <c r="J6" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K6" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01847971029054019</v>
+        <v>0.02273872765450446</v>
       </c>
       <c r="M6" t="n">
-        <v>3.460070166979522</v>
+        <v>3.478202726068979</v>
       </c>
       <c r="N6" t="n">
-        <v>18.6242712387131</v>
+        <v>18.68082925702614</v>
       </c>
       <c r="O6" t="n">
-        <v>4.315584692566362</v>
+        <v>4.322132489527148</v>
       </c>
       <c r="P6" t="n">
-        <v>395.5160982286322</v>
+        <v>395.6066406601719</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17033,28 +17171,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1083496187181136</v>
+        <v>-0.1150618646422726</v>
       </c>
       <c r="J7" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K7" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0336847454345115</v>
+        <v>0.03825675164030928</v>
       </c>
       <c r="M7" t="n">
-        <v>3.378310616938016</v>
+        <v>3.386827072841974</v>
       </c>
       <c r="N7" t="n">
-        <v>18.66177840797157</v>
+        <v>18.63355530445973</v>
       </c>
       <c r="O7" t="n">
-        <v>4.319928055879122</v>
+        <v>4.316660202570934</v>
       </c>
       <c r="P7" t="n">
-        <v>392.8446817369195</v>
+        <v>392.9156498893716</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17111,28 +17249,28 @@
         <v>0.1395</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1606608474946791</v>
+        <v>-0.1638465097364205</v>
       </c>
       <c r="J8" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K8" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1061530896348746</v>
+        <v>0.1115461666201483</v>
       </c>
       <c r="M8" t="n">
-        <v>2.740572207885894</v>
+        <v>2.735003583621297</v>
       </c>
       <c r="N8" t="n">
-        <v>12.04379345633051</v>
+        <v>11.9711662224751</v>
       </c>
       <c r="O8" t="n">
-        <v>3.470416899499325</v>
+        <v>3.459937314818738</v>
       </c>
       <c r="P8" t="n">
-        <v>394.1208016777498</v>
+        <v>394.1544905425703</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -17189,28 +17327,28 @@
         <v>0.1819</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1626806026607004</v>
+        <v>-0.165693721224615</v>
       </c>
       <c r="J9" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K9" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07161301650161744</v>
+        <v>0.07530166605437083</v>
       </c>
       <c r="M9" t="n">
-        <v>3.468969791846584</v>
+        <v>3.454388384440171</v>
       </c>
       <c r="N9" t="n">
-        <v>19.19773859660985</v>
+        <v>19.05867866294339</v>
       </c>
       <c r="O9" t="n">
-        <v>4.381522406265869</v>
+        <v>4.365624658962722</v>
       </c>
       <c r="P9" t="n">
-        <v>399.5117072069353</v>
+        <v>399.5433390287128</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -17248,7 +17386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J345"/>
+  <dimension ref="A1:J348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35179,6 +35317,162 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-36.60210203437236,175.54313453174774</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-36.60254570789045,175.5436877791274</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-36.602777696142276,175.54443888648171</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-36.602933696899136,175.54526268428657</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-36.60299128252598,175.5461116348086</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-36.60299673107673,175.5469789557133</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-36.60287828585347,175.54782714742018</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-36.60265744306078,175.54866200035872</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-36.602094905352644,175.54314354559426</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-36.602542893330245,175.54368999433038</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-36.60277320169749,175.5444405260634</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-36.6029382499591,175.5452619185219</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-36.60298930048585,175.5461116353694</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-36.60299619336804,175.54697888698897</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-36.60288373783872,175.54782865444207</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-36.60265631614603,175.54866160467165</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-36.60209805978622,175.54313955716682</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-36.60254798996627,175.54368598301676</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-36.60277449817196,175.54444005310717</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-36.60294476708412,175.54526082242722</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-36.603003264859396,175.54611163141826</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-36.60300587212459,175.5469801240271</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-36.60288927775916,175.54783018577098</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-36.60265752974654,175.54866203079618</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0140/nzd0140.xlsx
+++ b/data/nzd0140/nzd0140.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J348"/>
+  <dimension ref="A1:J350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12964,6 +12964,78 @@
         <v>393.34</v>
       </c>
       <c r="J348" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>385</v>
+      </c>
+      <c r="C349" t="n">
+        <v>388.99</v>
+      </c>
+      <c r="D349" t="n">
+        <v>388.09</v>
+      </c>
+      <c r="E349" t="n">
+        <v>385.96</v>
+      </c>
+      <c r="F349" t="n">
+        <v>387.29</v>
+      </c>
+      <c r="G349" t="n">
+        <v>385.41</v>
+      </c>
+      <c r="H349" t="n">
+        <v>387.57</v>
+      </c>
+      <c r="I349" t="n">
+        <v>393.32</v>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>385.44</v>
+      </c>
+      <c r="C350" t="n">
+        <v>389.33</v>
+      </c>
+      <c r="D350" t="n">
+        <v>389.39</v>
+      </c>
+      <c r="E350" t="n">
+        <v>385.95</v>
+      </c>
+      <c r="F350" t="n">
+        <v>386.69</v>
+      </c>
+      <c r="G350" t="n">
+        <v>384.79</v>
+      </c>
+      <c r="H350" t="n">
+        <v>387.17</v>
+      </c>
+      <c r="I350" t="n">
+        <v>393.51</v>
+      </c>
+      <c r="J350" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12980,7 +13052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B363"/>
+  <dimension ref="A1:B365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16613,6 +16685,26 @@
       </c>
       <c r="B363" t="n">
         <v>-0.64</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -16781,28 +16873,28 @@
         <v>0.1057</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1089721190552594</v>
+        <v>-0.1154761865320747</v>
       </c>
       <c r="J2" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K2" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04121054382977174</v>
+        <v>0.0460426845742633</v>
       </c>
       <c r="M2" t="n">
-        <v>2.66017704360674</v>
+        <v>2.674077230387254</v>
       </c>
       <c r="N2" t="n">
-        <v>15.61819678760648</v>
+        <v>15.72232283441463</v>
       </c>
       <c r="O2" t="n">
-        <v>3.951986435655679</v>
+        <v>3.965138438240792</v>
       </c>
       <c r="P2" t="n">
-        <v>393.9910575633277</v>
+        <v>394.0595236139955</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16859,28 +16951,28 @@
         <v>0.1009</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.140206837836549</v>
+        <v>-0.1439412352582168</v>
       </c>
       <c r="J3" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K3" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08084191273691477</v>
+        <v>0.08540398621195711</v>
       </c>
       <c r="M3" t="n">
-        <v>2.50764345860744</v>
+        <v>2.509032918367049</v>
       </c>
       <c r="N3" t="n">
-        <v>12.63505729837078</v>
+        <v>12.6265630304457</v>
       </c>
       <c r="O3" t="n">
-        <v>3.554582577233335</v>
+        <v>3.553387542957523</v>
       </c>
       <c r="P3" t="n">
-        <v>396.2740582498038</v>
+        <v>396.3133686880891</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16937,28 +17029,28 @@
         <v>0.1948</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04063931809284634</v>
+        <v>-0.04721539938069404</v>
       </c>
       <c r="J4" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K4" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008378126045600842</v>
+        <v>0.01121281012570718</v>
       </c>
       <c r="M4" t="n">
-        <v>2.588598994815945</v>
+        <v>2.60552918111254</v>
       </c>
       <c r="N4" t="n">
-        <v>11.05038036052482</v>
+        <v>11.18714420863929</v>
       </c>
       <c r="O4" t="n">
-        <v>3.324211238854237</v>
+        <v>3.344718853452303</v>
       </c>
       <c r="P4" t="n">
-        <v>395.7544541611751</v>
+        <v>395.8236758583312</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17015,28 +17107,28 @@
         <v>0.1976</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08199711011431036</v>
+        <v>-0.09063559024438575</v>
       </c>
       <c r="J5" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K5" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02136541328138541</v>
+        <v>0.02580118774695839</v>
       </c>
       <c r="M5" t="n">
-        <v>3.303404937571221</v>
+        <v>3.330850026386648</v>
       </c>
       <c r="N5" t="n">
-        <v>17.40971051581432</v>
+        <v>17.650985953132</v>
       </c>
       <c r="O5" t="n">
-        <v>4.172494519566721</v>
+        <v>4.201307647998656</v>
       </c>
       <c r="P5" t="n">
-        <v>395.9324842944035</v>
+        <v>396.0234202636566</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17093,28 +17185,28 @@
         <v>0.1302</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08811196425305361</v>
+        <v>-0.09512302507368812</v>
       </c>
       <c r="J6" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K6" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02273872765450446</v>
+        <v>0.02641603778276469</v>
       </c>
       <c r="M6" t="n">
-        <v>3.478202726068979</v>
+        <v>3.497790354390093</v>
       </c>
       <c r="N6" t="n">
-        <v>18.68082925702614</v>
+        <v>18.79548324882196</v>
       </c>
       <c r="O6" t="n">
-        <v>4.322132489527148</v>
+        <v>4.335375790957683</v>
       </c>
       <c r="P6" t="n">
-        <v>395.6066406601719</v>
+        <v>395.680962916335</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17171,28 +17263,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1150618646422726</v>
+        <v>-0.1203680031321205</v>
       </c>
       <c r="J7" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K7" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03825675164030928</v>
+        <v>0.04193943978045367</v>
       </c>
       <c r="M7" t="n">
-        <v>3.386827072841974</v>
+        <v>3.397381638664366</v>
       </c>
       <c r="N7" t="n">
-        <v>18.63355530445973</v>
+        <v>18.65386823868947</v>
       </c>
       <c r="O7" t="n">
-        <v>4.316660202570934</v>
+        <v>4.319012414741299</v>
       </c>
       <c r="P7" t="n">
-        <v>392.9156498893716</v>
+        <v>392.9718992008436</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17249,28 +17341,28 @@
         <v>0.1395</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1638465097364205</v>
+        <v>-0.1665428174527154</v>
       </c>
       <c r="J8" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K8" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1115461666201483</v>
+        <v>0.1158082686960631</v>
       </c>
       <c r="M8" t="n">
-        <v>2.735003583621297</v>
+        <v>2.734533561500066</v>
       </c>
       <c r="N8" t="n">
-        <v>11.9711662224751</v>
+        <v>11.93534977858549</v>
       </c>
       <c r="O8" t="n">
-        <v>3.459937314818738</v>
+        <v>3.454757557135593</v>
       </c>
       <c r="P8" t="n">
-        <v>394.1544905425703</v>
+        <v>394.1830738073775</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -17327,28 +17419,28 @@
         <v>0.1819</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.165693721224615</v>
+        <v>-0.1675827121449119</v>
       </c>
       <c r="J9" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K9" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07530166605437083</v>
+        <v>0.07771675789034826</v>
       </c>
       <c r="M9" t="n">
-        <v>3.454388384440171</v>
+        <v>3.444232293600034</v>
       </c>
       <c r="N9" t="n">
-        <v>19.05867866294339</v>
+        <v>18.96581937212141</v>
       </c>
       <c r="O9" t="n">
-        <v>4.365624658962722</v>
+        <v>4.354976391683588</v>
       </c>
       <c r="P9" t="n">
-        <v>399.5433390287128</v>
+        <v>399.5632236122794</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -17386,7 +17478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J348"/>
+  <dimension ref="A1:J350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35473,6 +35565,110 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-36.602116418587194,175.54311634451253</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-36.60255407550168,175.54368119338793</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-36.602788586527645,175.5444349136484</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-36.6029738709574,175.54525592753694</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-36.60300425587946,175.54611163113785</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-36.60300497594345,175.5469800094865</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-36.60288725524853,175.54782962671436</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-36.60265770311804,175.5486620916711</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-36.60211364268628,175.54311985433037</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-36.60255148914917,175.54368322898029</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-36.602777350415764,175.5444390126034</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-36.60297396023309,175.54525591252195</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-36.603009661443394,175.54611162960842</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-36.60301053226664,175.54698071963816</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-36.60289077265833,175.54783059898676</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-36.60265605608877,175.5486615133593</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
